--- a/dollarexpress/resources/sample/dollarexpress/dollarExpressControl.xlsx
+++ b/dollarexpress/resources/sample/dollarexpress/dollarExpressControl.xlsx
@@ -1,29 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\dollarexpress\resources\sample\dollarexpress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7B1D1A-DBA1-458E-9430-39682C828AF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C8EFEF-8410-4496-AB10-C0F0673F9537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DollarExpressControlConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="DollarExpressControl" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -33,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{D7C1663E-E325-4BAC-B97B-C15DE507DFCA}">
       <text>
         <r>
           <rPr>
@@ -57,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{2AA8C363-007B-41B6-B7EC-1044B3253B5E}">
       <text>
         <r>
           <rPr>
@@ -86,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>sid</t>
   </si>
@@ -94,63 +86,9 @@
     <t>说明</t>
   </si>
   <si>
-    <t>轴_1权重</t>
-  </si>
-  <si>
-    <t>轴_2权重</t>
-  </si>
-  <si>
-    <t>轴_3权重</t>
-  </si>
-  <si>
-    <t>轴_4权重</t>
-  </si>
-  <si>
-    <t>轴_5权重</t>
-  </si>
-  <si>
-    <t>轴_6权重</t>
-  </si>
-  <si>
-    <t>轴_7权重</t>
-  </si>
-  <si>
-    <t>拉火车</t>
-  </si>
-  <si>
-    <t>保险箱</t>
-  </si>
-  <si>
-    <t>免费</t>
-  </si>
-  <si>
-    <t>金火车</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>axle_1</t>
-  </si>
-  <si>
-    <t>axle_2</t>
-  </si>
-  <si>
-    <t>axle_3</t>
-  </si>
-  <si>
-    <t>axle_4</t>
-  </si>
-  <si>
-    <t>axle_5</t>
-  </si>
-  <si>
-    <t>axle_6</t>
-  </si>
-  <si>
-    <t>axle_7</t>
-  </si>
-  <si>
     <t>放水池+3</t>
   </si>
   <si>
@@ -172,86 +110,86 @@
     <t>吸水池-3</t>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>进入条件最小值</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>进入条件最大值</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ntryConditionMin</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>entryConditionMax</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ong</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ong</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>special_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>special_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>special_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>special_4</t>
+    <t>中奖图标含四色火车图标</t>
+  </si>
+  <si>
+    <t>最后一列含保险箱</t>
+  </si>
+  <si>
+    <t>含3个以上免费</t>
+  </si>
+  <si>
+    <t>最后一列含金火车</t>
+  </si>
+  <si>
+    <t>describe</t>
+  </si>
+  <si>
+    <t>进入最低条件</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入最高条件</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规赔率权重</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>entryConditionMin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>axleList</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000,0,0,0,0,0,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000,10000,0,0,0,0,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,5000,10000,5000,0,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,5000,10000,0,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,1000,5000,10000,0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{,}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>safeBox</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>free</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>goldTrain</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>train</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -347,7 +285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -365,6 +303,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,20 +797,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="17.5" customWidth="1"/>
-    <col min="14" max="14" width="13.625" customWidth="1"/>
-    <col min="15" max="15" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="27.125" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,461 +817,287 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>38</v>
+      <c r="H3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="7"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
         <v>2001</v>
       </c>
-      <c r="D4">
-        <v>99999999</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="D5">
+        <v>999999</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6">
         <v>2</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5">
-        <v>1001</v>
-      </c>
-      <c r="D5">
-        <v>2000</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>500</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>500</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>-499</v>
+      </c>
+      <c r="D8">
+        <v>499</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>-499</v>
-      </c>
-      <c r="D7">
-        <v>499</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>-1000</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-500</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>-1000</v>
-      </c>
-      <c r="D8">
-        <v>-500</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>-2000</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1001</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>-999999</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2001</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9">
-        <v>-2000</v>
-      </c>
-      <c r="D9">
-        <v>-1001</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10">
-        <v>-2001</v>
-      </c>
-      <c r="D10">
-        <v>-99999999</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
     </row>
